--- a/output/docs/DOC_069_DAST_report.xlsx
+++ b/output/docs/DOC_069_DAST_report.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>FND-0011</t>
+          <t>FND-0009</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>GET /api/items/{id}</t>
+          <t>GET /api/exams/{id}</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>object-level authorization not enforced (IDOR) on sample endpoint</t>
+          <t>object-level authorization not enforced (sonoA read sonoB's exam)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -574,44 +574,118 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>FND-0010</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>CWE-306</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>GET /api/frame/{id}</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>frame/PHI endpoint reachable without authentication</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>FND-0011</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>CWE-20</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>POST /api/patient</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>empty/whitespace patient identity accepted (unattributable record)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
           <t>FND-0012</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>CWE-306</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>WS /realtime</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>websocket endpoint reachable without authentication</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CWE-20</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/patient</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>duplicate patientId silently overwrites demographics</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Remediate / upgrade; verified on retest.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Total findings: 2</t>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Total findings: 4</t>
         </is>
       </c>
     </row>
